--- a/Dashboards/data/Data final/ingresos/ingresos_series.xlsx
+++ b/Dashboards/data/Data final/ingresos/ingresos_series.xlsx
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>207.49</v>
+        <v>210.94</v>
       </c>
     </row>
     <row r="37">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>90.31</v>
+        <v>91.81</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>222.21</v>
+        <v>223.77</v>
       </c>
     </row>
     <row r="39">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>93.23</v>
+        <v>93.88</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>219.83</v>
+        <v>220.42</v>
       </c>
     </row>
     <row r="41">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>91</v>
+        <v>91.25</v>
       </c>
     </row>
     <row r="42">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>219.7</v>
+        <v>211.07</v>
       </c>
     </row>
     <row r="43">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>90.47</v>
+        <v>86.92</v>
       </c>
     </row>
     <row r="44">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>233.23</v>
+        <v>245.33</v>
       </c>
     </row>
     <row r="45">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>94.23999999999999</v>
+        <v>99.13</v>
       </c>
     </row>
   </sheetData>
